--- a/src/nodes/HPC/compresor_blade_self_frequency.xlsx
+++ b/src/nodes/HPC/compresor_blade_self_frequency.xlsx
@@ -552,58 +552,58 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>375.79988550685783</v>
+        <v>290.31431070612922</v>
       </c>
       <c r="C3">
-        <v>2355.2676653794929</v>
+        <v>1819.5000455650852</v>
       </c>
       <c r="D3">
-        <v>6595.4810682754205</v>
+        <v>5095.16530993398</v>
       </c>
       <c r="E3">
-        <v>12934.196948289366</v>
+        <v>9991.9734315922869</v>
       </c>
       <c r="F3">
-        <v>21372.381522001622</v>
+        <v>16510.670835728837</v>
       </c>
       <c r="G3">
-        <v>31918.434000364356</v>
+        <v>24657.746111702203</v>
       </c>
       <c r="H3">
-        <v>1176.4169094719168</v>
+        <v>852.26518743295708</v>
       </c>
       <c r="I3">
-        <v>3529.2507284157509</v>
+        <v>2556.7955622988716</v>
       </c>
       <c r="J3">
-        <v>5882.0845473595846</v>
+        <v>4261.3259371647855</v>
       </c>
       <c r="K3">
-        <v>8234.9183663034182</v>
+        <v>5965.8563120307</v>
       </c>
       <c r="L3">
-        <v>10587.752185247251</v>
+        <v>7670.3866868966134</v>
       </c>
       <c r="M3">
-        <v>12940.586004191086</v>
+        <v>9374.9170617625277</v>
       </c>
       <c r="N3">
-        <v>2352.8338189438336</v>
+        <v>1704.5303748659142</v>
       </c>
       <c r="O3">
-        <v>4705.6676378876673</v>
+        <v>3409.0607497318283</v>
       </c>
       <c r="P3">
-        <v>7058.5014568315019</v>
+        <v>5113.5911245977431</v>
       </c>
       <c r="Q3">
-        <v>9411.3352757753346</v>
+        <v>6818.1214994636566</v>
       </c>
       <c r="R3">
-        <v>11764.169094719169</v>
+        <v>8522.651874329571</v>
       </c>
       <c r="S3">
-        <v>14117.002913663004</v>
+        <v>10227.182249195486</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -611,58 +611,58 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>485.47457383405538</v>
+        <v>376.82866942135126</v>
       </c>
       <c r="C4">
-        <v>3042.6368134015147</v>
+        <v>2361.7154094632915</v>
       </c>
       <c r="D4">
-        <v>8520.328196835384</v>
+        <v>6613.5367545410936</v>
       </c>
       <c r="E4">
-        <v>16708.955998981888</v>
+        <v>12969.605404439752</v>
       </c>
       <c r="F4">
-        <v>27609.768420281314</v>
+        <v>21430.890220839028</v>
       </c>
       <c r="G4">
-        <v>41233.6159253421</v>
+        <v>32005.813408240196</v>
       </c>
       <c r="H4">
-        <v>1404.7439875395812</v>
+        <v>1017.6786409479544</v>
       </c>
       <c r="I4">
-        <v>4214.2319626187436</v>
+        <v>3053.0359228438629</v>
       </c>
       <c r="J4">
-        <v>7023.7199376979061</v>
+        <v>5088.3932047397711</v>
       </c>
       <c r="K4">
-        <v>9833.2079127770685</v>
+        <v>7123.75048663568</v>
       </c>
       <c r="L4">
-        <v>12642.695887856231</v>
+        <v>9159.10776853159</v>
       </c>
       <c r="M4">
-        <v>15452.183862935393</v>
+        <v>11194.465050427498</v>
       </c>
       <c r="N4">
-        <v>2809.4879750791624</v>
+        <v>2035.3572818959087</v>
       </c>
       <c r="O4">
-        <v>5618.9759501583248</v>
+        <v>4070.7145637918175</v>
       </c>
       <c r="P4">
-        <v>8428.4639252374873</v>
+        <v>6106.0718456877257</v>
       </c>
       <c r="Q4">
-        <v>11237.95190031665</v>
+        <v>8141.4291275836349</v>
       </c>
       <c r="R4">
-        <v>14047.439875395812</v>
+        <v>10176.786409479542</v>
       </c>
       <c r="S4">
-        <v>16856.927850474975</v>
+        <v>12212.143691375452</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -670,58 +670,58 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>599.00889348154271</v>
+        <v>468.7237502830244</v>
       </c>
       <c r="C5">
-        <v>3754.1956038357571</v>
+        <v>2937.6536172916781</v>
       </c>
       <c r="D5">
-        <v>10512.913838059239</v>
+        <v>8226.3426373138918</v>
       </c>
       <c r="E5">
-        <v>20616.554982760295</v>
+        <v>16132.429876407738</v>
       </c>
       <c r="F5">
-        <v>34066.659145711579</v>
+        <v>26657.12046708275</v>
       </c>
       <c r="G5">
-        <v>50876.614308795477</v>
+        <v>39810.890489318583</v>
       </c>
       <c r="H5">
-        <v>1648.200639592425</v>
+        <v>1194.0528032656057</v>
       </c>
       <c r="I5">
-        <v>4944.6019187772754</v>
+        <v>3582.1584097968171</v>
       </c>
       <c r="J5">
-        <v>8241.0031979621253</v>
+        <v>5970.2640163280284</v>
       </c>
       <c r="K5">
-        <v>11537.404477146974</v>
+        <v>8358.36962285924</v>
       </c>
       <c r="L5">
-        <v>14833.805756331825</v>
+        <v>10746.475229390451</v>
       </c>
       <c r="M5">
-        <v>18130.207035516672</v>
+        <v>13134.580835921661</v>
       </c>
       <c r="N5">
-        <v>3296.40127918485</v>
+        <v>2388.1056065312114</v>
       </c>
       <c r="O5">
-        <v>6592.8025583697</v>
+        <v>4776.2112130624228</v>
       </c>
       <c r="P5">
-        <v>9889.20383755455</v>
+        <v>7164.3168195936341</v>
       </c>
       <c r="Q5">
-        <v>13185.6051167394</v>
+        <v>9552.4224261248455</v>
       </c>
       <c r="R5">
-        <v>16482.006395924251</v>
+        <v>11940.528032656057</v>
       </c>
       <c r="S5">
-        <v>19778.4076751091</v>
+        <v>14328.633639187268</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -729,58 +729,58 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>696.398156993768</v>
+        <v>542.88192416326592</v>
       </c>
       <c r="C6">
-        <v>4364.5677517572367</v>
+        <v>3402.4285036068986</v>
       </c>
       <c r="D6">
-        <v>12222.145449138179</v>
+        <v>9527.85668973391</v>
       </c>
       <c r="E6">
-        <v>23968.477012265506</v>
+        <v>18684.789425423693</v>
       </c>
       <c r="F6">
-        <v>39605.352945798026</v>
+        <v>30874.622510772257</v>
       </c>
       <c r="G6">
-        <v>59148.337903299682</v>
+        <v>46109.489477425079</v>
       </c>
       <c r="H6">
-        <v>1865.6237856648188</v>
+        <v>1351.5668631617573</v>
       </c>
       <c r="I6">
-        <v>5596.8713569944566</v>
+        <v>4054.7005894852723</v>
       </c>
       <c r="J6">
-        <v>9328.1189283240947</v>
+        <v>6757.8343158087873</v>
       </c>
       <c r="K6">
-        <v>13059.36649965373</v>
+        <v>9460.968042132301</v>
       </c>
       <c r="L6">
-        <v>16790.614070983367</v>
+        <v>12164.101768455816</v>
       </c>
       <c r="M6">
-        <v>20521.861642313008</v>
+        <v>14867.235494779332</v>
       </c>
       <c r="N6">
-        <v>3731.2475713296376</v>
+        <v>2703.1337263235146</v>
       </c>
       <c r="O6">
-        <v>7462.4951426592752</v>
+        <v>5406.2674526470291</v>
       </c>
       <c r="P6">
-        <v>11193.742713988913</v>
+        <v>8109.4011789705446</v>
       </c>
       <c r="Q6">
-        <v>14924.99028531855</v>
+        <v>10812.534905294058</v>
       </c>
       <c r="R6">
-        <v>18656.237856648189</v>
+        <v>13515.668631617575</v>
       </c>
       <c r="S6">
-        <v>22387.485427977826</v>
+        <v>16218.802357941089</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -788,58 +788,58 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>802.81285263446591</v>
+        <v>624.88399618250924</v>
       </c>
       <c r="C7">
-        <v>5031.5053997708692</v>
+        <v>3916.3638084581821</v>
       </c>
       <c r="D7">
-        <v>14089.778031138278</v>
+        <v>10967.035184513967</v>
       </c>
       <c r="E7">
-        <v>27631.034359116904</v>
+        <v>21507.118517499337</v>
       </c>
       <c r="F7">
-        <v>45657.338490480091</v>
+        <v>35538.220442491</v>
       </c>
       <c r="G7">
-        <v>68186.633470887071</v>
+        <v>53074.307255666739</v>
       </c>
       <c r="H7">
-        <v>2079.2606225202803</v>
+        <v>1506.3378841291112</v>
       </c>
       <c r="I7">
-        <v>6237.7818675608414</v>
+        <v>4519.0136523873343</v>
       </c>
       <c r="J7">
-        <v>10396.303112601403</v>
+        <v>7531.6894206455572</v>
       </c>
       <c r="K7">
-        <v>14554.824357641963</v>
+        <v>10544.365188903779</v>
       </c>
       <c r="L7">
-        <v>18713.345602682526</v>
+        <v>13557.040957162004</v>
       </c>
       <c r="M7">
-        <v>22871.866847723086</v>
+        <v>16569.716725420225</v>
       </c>
       <c r="N7">
-        <v>4158.5212450405606</v>
+        <v>3012.6757682582224</v>
       </c>
       <c r="O7">
-        <v>8317.0424900811213</v>
+        <v>6025.3515365164449</v>
       </c>
       <c r="P7">
-        <v>12475.563735121683</v>
+        <v>9038.0273047746687</v>
       </c>
       <c r="Q7">
-        <v>16634.084980162243</v>
+        <v>12050.70307303289</v>
       </c>
       <c r="R7">
-        <v>20792.606225202806</v>
+        <v>15063.378841291114</v>
       </c>
       <c r="S7">
-        <v>24951.127470243366</v>
+        <v>18076.054609549337</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -847,58 +847,58 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>909.00258337855882</v>
+        <v>703.18889436527786</v>
       </c>
       <c r="C8">
-        <v>5697.0331150856009</v>
+        <v>4407.127648053186</v>
       </c>
       <c r="D8">
-        <v>15953.462363620994</v>
+        <v>12341.326378938133</v>
       </c>
       <c r="E8">
-        <v>31285.848914149155</v>
+        <v>24202.199102065384</v>
       </c>
       <c r="F8">
-        <v>51696.529897152206</v>
+        <v>39991.55378171333</v>
       </c>
       <c r="G8">
-        <v>77205.821722369219</v>
+        <v>59725.106845935217</v>
       </c>
       <c r="H8">
-        <v>2290.824770771907</v>
+        <v>1659.6073807954558</v>
       </c>
       <c r="I8">
-        <v>6872.4743123157214</v>
+        <v>4978.8221423863679</v>
       </c>
       <c r="J8">
-        <v>11454.123853859535</v>
+        <v>8298.03690397728</v>
       </c>
       <c r="K8">
-        <v>16035.77339540335</v>
+        <v>11617.251665568192</v>
       </c>
       <c r="L8">
-        <v>20617.422936947165</v>
+        <v>14936.466427159103</v>
       </c>
       <c r="M8">
-        <v>25199.07247849098</v>
+        <v>18255.681188750015</v>
       </c>
       <c r="N8">
-        <v>4581.6495415438139</v>
+        <v>3319.2147615909116</v>
       </c>
       <c r="O8">
-        <v>9163.2990830876279</v>
+        <v>6638.4295231818232</v>
       </c>
       <c r="P8">
-        <v>13744.948624631443</v>
+        <v>9957.6442847727358</v>
       </c>
       <c r="Q8">
-        <v>18326.598166175256</v>
+        <v>13276.859046363647</v>
       </c>
       <c r="R8">
-        <v>22908.247707719071</v>
+        <v>16596.073807954559</v>
       </c>
       <c r="S8">
-        <v>27489.897249262885</v>
+        <v>19915.288569545472</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -906,58 +906,58 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>997.84806652900625</v>
+        <v>758.74950061951813</v>
       </c>
       <c r="C9">
-        <v>6253.858440875777</v>
+        <v>4755.3451553656141</v>
       </c>
       <c r="D9">
-        <v>17512.746239746244</v>
+        <v>13316.443564504865</v>
       </c>
       <c r="E9">
-        <v>34343.713009780549</v>
+        <v>26114.471701322436</v>
       </c>
       <c r="F9">
-        <v>56749.324311490243</v>
+        <v>43151.380381601055</v>
       </c>
       <c r="G9">
-        <v>84751.882270906266</v>
+        <v>64444.127825290569</v>
       </c>
       <c r="H9">
-        <v>2479.7721694272791</v>
+        <v>1796.4928565377422</v>
       </c>
       <c r="I9">
-        <v>7439.3165082818377</v>
+        <v>5389.4785696132258</v>
       </c>
       <c r="J9">
-        <v>12398.860847136395</v>
+        <v>8982.46428268871</v>
       </c>
       <c r="K9">
-        <v>17358.405185990952</v>
+        <v>12575.449995764193</v>
       </c>
       <c r="L9">
-        <v>22317.949524845513</v>
+        <v>16168.435708839679</v>
       </c>
       <c r="M9">
-        <v>27277.493863700071</v>
+        <v>19761.421421915162</v>
       </c>
       <c r="N9">
-        <v>4959.5443388545582</v>
+        <v>3592.9857130754845</v>
       </c>
       <c r="O9">
-        <v>9919.0886777091164</v>
+        <v>7185.9714261509689</v>
       </c>
       <c r="P9">
-        <v>14878.633016563676</v>
+        <v>10778.957139226452</v>
       </c>
       <c r="Q9">
-        <v>19838.177355418233</v>
+        <v>14371.942852301938</v>
       </c>
       <c r="R9">
-        <v>24797.72169427279</v>
+        <v>17964.92856537742</v>
       </c>
       <c r="S9">
-        <v>29757.266033127351</v>
+        <v>21557.914278452903</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -965,58 +965,58 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>1083.1896407042209</v>
+        <v>814.23021348102861</v>
       </c>
       <c r="C10">
-        <v>6788.7235590393129</v>
+        <v>5103.0619431945315</v>
       </c>
       <c r="D10">
-        <v>19010.534713125595</v>
+        <v>14290.158579981737</v>
       </c>
       <c r="E10">
-        <v>37280.980344948832</v>
+        <v>28023.994547542603</v>
       </c>
       <c r="F10">
-        <v>61602.845436172989</v>
+        <v>46306.663307750823</v>
       </c>
       <c r="G10">
-        <v>92000.339515976608</v>
+        <v>69156.363086817728</v>
       </c>
       <c r="H10">
-        <v>2627.0449592516634</v>
+        <v>1903.1859535804524</v>
       </c>
       <c r="I10">
-        <v>7881.1348777549911</v>
+        <v>5709.5578607413572</v>
       </c>
       <c r="J10">
-        <v>13135.224796258317</v>
+        <v>9515.929767902262</v>
       </c>
       <c r="K10">
-        <v>18389.314714761644</v>
+        <v>13322.301675063167</v>
       </c>
       <c r="L10">
-        <v>23643.40463326497</v>
+        <v>17128.67358222407</v>
       </c>
       <c r="M10">
-        <v>28897.494551768297</v>
+        <v>20935.045489384975</v>
       </c>
       <c r="N10">
-        <v>5254.0899185033268</v>
+        <v>3806.3719071609048</v>
       </c>
       <c r="O10">
-        <v>10508.179837006654</v>
+        <v>7612.74381432181</v>
       </c>
       <c r="P10">
-        <v>15762.269755509982</v>
+        <v>11419.115721482714</v>
       </c>
       <c r="Q10">
-        <v>21016.359674013307</v>
+        <v>15225.487628643619</v>
       </c>
       <c r="R10">
-        <v>26270.449592516634</v>
+        <v>19031.859535804524</v>
       </c>
       <c r="S10">
-        <v>31524.539511019964</v>
+        <v>22838.231442965429</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -1024,58 +1024,58 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>893.642997102279</v>
+        <v>669.42052086831166</v>
       </c>
       <c r="C11">
-        <v>5600.7692834419677</v>
+        <v>4195.4895894023912</v>
       </c>
       <c r="D11">
-        <v>15683.893733058178</v>
+        <v>11748.674074626482</v>
       </c>
       <c r="E11">
-        <v>30757.206086933551</v>
+        <v>23039.966727129802</v>
       </c>
       <c r="F11">
-        <v>50823.003984620329</v>
+        <v>38071.088689550765</v>
       </c>
       <c r="G11">
-        <v>75901.260545691068</v>
+        <v>56857.00165929088</v>
       </c>
       <c r="H11">
-        <v>2089.0972420864678</v>
+        <v>1513.4646084021522</v>
       </c>
       <c r="I11">
-        <v>6267.2917262594019</v>
+        <v>4540.3938252064554</v>
       </c>
       <c r="J11">
-        <v>10445.486210432338</v>
+        <v>7567.32304201076</v>
       </c>
       <c r="K11">
-        <v>14623.680694605273</v>
+        <v>10594.252258815064</v>
       </c>
       <c r="L11">
-        <v>18801.875178778209</v>
+        <v>13621.181475619369</v>
       </c>
       <c r="M11">
-        <v>22980.069662951144</v>
+        <v>16648.110692423674</v>
       </c>
       <c r="N11">
-        <v>4178.1944841729355</v>
+        <v>3026.9292168043044</v>
       </c>
       <c r="O11">
-        <v>8356.388968345871</v>
+        <v>6053.8584336086087</v>
       </c>
       <c r="P11">
-        <v>12534.583452518804</v>
+        <v>9080.78765041291</v>
       </c>
       <c r="Q11">
-        <v>16712.777936691742</v>
+        <v>12107.716867217217</v>
       </c>
       <c r="R11">
-        <v>20890.972420864677</v>
+        <v>15134.64608402152</v>
       </c>
       <c r="S11">
-        <v>25069.166905037608</v>
+        <v>18161.575300825822</v>
       </c>
     </row>
   </sheetData>
